--- a/ZonasEscolares/excels/ICA-ICA-PARCONA.xlsx
+++ b/ZonasEscolares/excels/ICA-ICA-PARCONA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/ICA-ICA-PARCONA.xlsx
+++ b/ZonasEscolares/excels/ICA-ICA-PARCONA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>22505</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-14.055103</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-75.722967</v>
-      </c>
-      <c r="I2" t="n">
-        <v>267</v>
-      </c>
-      <c r="J2" t="n">
-        <v>10</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-14.055103</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-75.722967</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>78</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-14.06801</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-75.68414799999999</v>
-      </c>
-      <c r="I3" t="n">
-        <v>159</v>
-      </c>
-      <c r="J3" t="n">
-        <v>6</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-14.06801</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-75.684148</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>11 / 22525</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-14.066025</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-75.721355</v>
-      </c>
-      <c r="I4" t="n">
-        <v>456</v>
-      </c>
-      <c r="J4" t="n">
-        <v>20</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-14.066025</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-75.721355</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>18 MARIA INMACULADA</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-14.05024</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-75.69891</v>
-      </c>
-      <c r="I5" t="n">
-        <v>366</v>
-      </c>
-      <c r="J5" t="n">
-        <v>20</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-14.05024</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-75.69891</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>66 VIRGEN DE LA ASUNCION</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-14.0414</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-75.69864</v>
-      </c>
-      <c r="I6" t="n">
-        <v>246</v>
-      </c>
-      <c r="J6" t="n">
-        <v>13</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-14.0414</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-75.69864</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>81</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-14.062823</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-75.72019400000001</v>
-      </c>
-      <c r="I7" t="n">
-        <v>173</v>
-      </c>
-      <c r="J7" t="n">
-        <v>9</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-14.062823</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-75.720194</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>173 / 22319</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-14.04821</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-75.7077</v>
-      </c>
-      <c r="I8" t="n">
-        <v>765</v>
-      </c>
-      <c r="J8" t="n">
-        <v>33</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-14.04821</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-75.7077</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>22320</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-14.04791</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-75.7068</v>
-      </c>
-      <c r="I9" t="n">
-        <v>548</v>
-      </c>
-      <c r="J9" t="n">
-        <v>27</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-14.04791</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-75.7068</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>22542</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-14.066236</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-75.72126400000001</v>
-      </c>
-      <c r="I10" t="n">
-        <v>222</v>
-      </c>
-      <c r="J10" t="n">
-        <v>10</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-14.066236</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-75.721264</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>22718 LUIS ABRAHAM ELIAS GHEZZI</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-14.05435</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-75.69898000000001</v>
-      </c>
-      <c r="I11" t="n">
-        <v>864</v>
-      </c>
-      <c r="J11" t="n">
-        <v>36</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-14.05435</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-75.69898</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>864</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>22321 ALBERTO CASAVILCA CURACCA</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-14.060111</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-75.723401</v>
-      </c>
-      <c r="I12" t="n">
-        <v>396</v>
-      </c>
-      <c r="J12" t="n">
-        <v>22</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-14.060111</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-75.723401</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>ABRAHAM VALDELOMAR</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-14.071959</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-75.718819</v>
-      </c>
-      <c r="I13" t="n">
-        <v>420</v>
-      </c>
-      <c r="J13" t="n">
-        <v>35</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-14.071959</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-75.718819</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>MI PEQUEÑO HOGAR</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-14.049314</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-75.702259</v>
-      </c>
-      <c r="I14" t="n">
-        <v>236</v>
-      </c>
-      <c r="J14" t="n">
-        <v>21</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-14.049314</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-75.702259</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>SACO OLIVEROS</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-14.044636</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-75.703337</v>
-      </c>
-      <c r="I15" t="n">
-        <v>432</v>
-      </c>
-      <c r="J15" t="n">
-        <v>31</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-14.044636</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-75.703337</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>DANIEL ALCIDES CARRION</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-14.045144</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-75.702316</v>
-      </c>
-      <c r="I16" t="n">
-        <v>265</v>
-      </c>
-      <c r="J16" t="n">
-        <v>29</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-14.045144</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-75.702316</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>MIGUEL GRAU</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-14.04626</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-75.69871999999999</v>
-      </c>
-      <c r="I17" t="n">
-        <v>97</v>
-      </c>
-      <c r="J17" t="n">
-        <v>10</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-14.04626</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-75.69872</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/ICA-ICA-PARCONA.xlsx
+++ b/ZonasEscolares/excels/ICA-ICA-PARCONA.xlsx
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>212115</t>
+          <t>212549</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>22542</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-14.06801</t>
+          <t>-14.066236</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-75.684148</t>
+          <t>-75.721264</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>222</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,37 +625,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>212403</t>
+          <t>635006</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>11 / 22525</t>
+          <t>MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-14.066025</t>
+          <t>-14.04626</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-75.721355</t>
+          <t>-75.69872</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>97</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>212422</t>
+          <t>212460</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>18 MARIA INMACULADA</t>
+          <t>66 VIRGEN DE LA ASUNCION</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-14.05024</t>
+          <t>-14.0414</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-75.69891</t>
+          <t>-75.69864</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>246</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>212460</t>
+          <t>212403</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>66 VIRGEN DE LA ASUNCION</t>
+          <t>11 / 22525</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-14.0414</t>
+          <t>-14.066025</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-75.69864</t>
+          <t>-75.721355</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>456</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,37 +811,37 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>212484</t>
+          <t>212422</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>18 MARIA INMACULADA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-14.062823</t>
+          <t>-14.05024</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-75.720194</t>
+          <t>-75.69891</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>366</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>212506</t>
+          <t>212648</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>173 / 22319</t>
+          <t>MI PEQUEÑO HOGAR</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-14.04821</t>
+          <t>-14.049314</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-75.7077</t>
+          <t>-75.702259</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>236</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>212511</t>
+          <t>212568</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>22320</t>
+          <t>22321 ALBERTO CASAVILCA CURACCA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-14.04791</t>
+          <t>-14.060111</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-75.7068</t>
+          <t>-75.723401</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>396</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>212549</t>
+          <t>212511</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>22542</t>
+          <t>22320</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-14.066236</t>
+          <t>-14.04791</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-75.721264</t>
+          <t>-75.7068</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>548</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>212554</t>
+          <t>634766</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>22718 LUIS ABRAHAM ELIAS GHEZZI</t>
+          <t>DANIEL ALCIDES CARRION</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-14.05435</t>
+          <t>-14.045144</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-75.69898</t>
+          <t>-75.702316</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>265</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>212568</t>
+          <t>212672</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>22321 ALBERTO CASAVILCA CURACCA</t>
+          <t>SACO OLIVEROS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-14.060111</t>
+          <t>-14.044636</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-75.723401</t>
+          <t>-75.703337</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>432</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>212592</t>
+          <t>212506</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ABRAHAM VALDELOMAR</t>
+          <t>173 / 22319</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-14.071959</t>
+          <t>-14.04821</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-75.718819</t>
+          <t>-75.7077</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>765</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>212648</t>
+          <t>212592</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MI PEQUEÑO HOGAR</t>
+          <t>ABRAHAM VALDELOMAR</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-14.049314</t>
+          <t>-14.071959</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-75.702259</t>
+          <t>-75.718819</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>420</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>212672</t>
+          <t>212554</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS</t>
+          <t>22718 LUIS ABRAHAM ELIAS GHEZZI</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-14.044636</t>
+          <t>-14.05435</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-75.703337</t>
+          <t>-75.69898</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>864</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,37 +1369,37 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>634766</t>
+          <t>212115</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>DANIEL ALCIDES CARRION</t>
+          <t>78</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-14.045144</t>
+          <t>-14.06801</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-75.702316</t>
+          <t>-75.684148</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>159</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>635006</t>
+          <t>212484</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MIGUEL GRAU</t>
+          <t>81</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-14.04626</t>
+          <t>-14.062823</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-75.69872</t>
+          <t>-75.720194</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>173</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">

--- a/ZonasEscolares/excels/ICA-ICA-PARCONA.xlsx
+++ b/ZonasEscolares/excels/ICA-ICA-PARCONA.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>211818</t>
+          <t>635006</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>22505</t>
+          <t>MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-14.055103</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-75.722967</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>-14.04626</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-75.69872</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>212549</t>
+          <t>634766</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>22542</t>
+          <t>DANIEL ALCIDES CARRION</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-14.066236</t>
+          <t>265</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-75.721264</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>-14.045144</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-75.702316</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,37 +625,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>635006</t>
+          <t>212672</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MIGUEL GRAU</t>
+          <t>SACO OLIVEROS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-14.04626</t>
+          <t>432</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-75.69872</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>-14.044636</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-75.703337</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>212460</t>
+          <t>212648</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>66 VIRGEN DE LA ASUNCION</t>
+          <t>MI PEQUEÑO HOGAR</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-14.0414</t>
+          <t>236</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-75.69864</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>-14.049314</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-75.702259</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>212403</t>
+          <t>212592</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>11 / 22525</t>
+          <t>ABRAHAM VALDELOMAR</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-14.066025</t>
+          <t>420</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-75.721355</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>-14.071959</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-75.718819</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>212422</t>
+          <t>212568</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18 MARIA INMACULADA</t>
+          <t>22321 ALBERTO CASAVILCA CURACCA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-14.05024</t>
+          <t>396</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-75.69891</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>-14.060111</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-75.723401</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>212648</t>
+          <t>212554</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MI PEQUEÑO HOGAR</t>
+          <t>22718 LUIS ABRAHAM ELIAS GHEZZI</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-14.049314</t>
+          <t>864</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-75.702259</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>-14.05435</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-75.69898</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>212568</t>
+          <t>212549</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>22321 ALBERTO CASAVILCA CURACCA</t>
+          <t>22542</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-14.060111</t>
+          <t>222</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-75.723401</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>-14.066236</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-75.721264</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1007,22 +1007,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>-14.04791</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>-75.7068</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>548</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>634766</t>
+          <t>212506</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>DANIEL ALCIDES CARRION</t>
+          <t>173 / 22319</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-14.045144</t>
+          <t>765</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-75.702316</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>-14.04821</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-75.7077</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,37 +1121,37 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>212672</t>
+          <t>212484</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS</t>
+          <t>81</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-14.044636</t>
+          <t>173</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-75.703337</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>-14.062823</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-75.720194</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>212506</t>
+          <t>212460</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>173 / 22319</t>
+          <t>66 VIRGEN DE LA ASUNCION</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-14.04821</t>
+          <t>246</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-75.7077</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>-14.0414</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-75.69864</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>212592</t>
+          <t>212422</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ABRAHAM VALDELOMAR</t>
+          <t>18 MARIA INMACULADA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-14.071959</t>
+          <t>366</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-75.718819</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>-14.05024</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-75.69891</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>212554</t>
+          <t>212403</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>22718 LUIS ABRAHAM ELIAS GHEZZI</t>
+          <t>11 / 22525</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-14.05435</t>
+          <t>456</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-75.69898</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>-14.066025</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-75.721355</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1379,22 +1379,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>-14.06801</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>-75.684148</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,37 +1431,37 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>212484</t>
+          <t>211818</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>22505</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-14.062823</t>
+          <t>267</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-75.720194</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>-14.055103</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-75.722967</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">

--- a/ZonasEscolares/excels/ICA-ICA-PARCONA.xlsx
+++ b/ZonasEscolares/excels/ICA-ICA-PARCONA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
